--- a/output/full_scan/batch_seq6_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq6_2026-06-18.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1141.88137953711</v>
+        <v>1281.88137953711</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>114</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>65.85770210135402</v>
+        <v>65.85770210235331</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>41.48546199880283</v>
+        <v>41.4854619749655</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.872381972630764</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1030614982762916</v>
+        <v>0.1030614984289304</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1059.613134038523</v>
+        <v>1259.613134038523</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>155.5</v>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>71.83714696706522</v>
+        <v>71.83714697168239</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>61.77269409868804</v>
+        <v>61.77269413266056</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.625049938328196</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,64 +623,64 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2684405773459257</v>
+        <v>0.2684405774413232</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6288</v>
+        <v>6182</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1053.76371134358</v>
+        <v>1090.972985131049</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>24.25</v>
+        <v>120</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.46726841884393</v>
+        <v>74.80141097666259</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>25.29949297338547</v>
+        <v>41.16547377113102</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.476371134358034</v>
+        <v>3.185114777399742</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1955033873733422</v>
+        <v>1.879788884226068</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>920.1023557284924</v>
+        <v>1080.102355728493</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>38.35</v>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.96435202465202</v>
+        <v>68.96435200147269</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>52.69632017704862</v>
+        <v>52.69632016694276</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>2.110235572849227</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.3932672570107829</v>
+        <v>0.3932672571252598</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6259</v>
+        <v>6208</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>919.9536395688672</v>
+        <v>1070.263952910117</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>35.85</v>
+        <v>99</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>74.09447065628481</v>
+        <v>59.43824753028846</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>47.28967310008448</v>
+        <v>24.93777213134326</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.095363956886709</v>
+        <v>3.93263461349321</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.6590754801553913</v>
+        <v>0.2644630702497279</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6208</v>
+        <v>6209</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>870.2639529101173</v>
+        <v>1050.633881032445</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>99</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>59.43824753072344</v>
+        <v>66.2170962499149</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>24.93777218384001</v>
+        <v>38.65150830177213</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.93263461349321</v>
+        <v>1.163388103244503</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2644630701447945</v>
+        <v>0.8478290929879462</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6446</v>
+        <v>6202</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>863.2103341579901</v>
+        <v>1041.641390576467</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1060</v>
+        <v>67</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>74.09915146258828</v>
+        <v>64.34662512514765</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>40.6352249165</v>
+        <v>19.9644913956534</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.877509351429905</v>
+        <v>1.933771881274046</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>3.156858669433817</v>
+        <v>1.10205100765132</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6209</v>
+        <v>6257</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>840.6338810324451</v>
+        <v>1004.010711332806</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>97.09999999999999</v>
+        <v>235</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>66.21709625634713</v>
+        <v>61.30340628238463</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>38.65150832581559</v>
+        <v>27.18010090578662</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.163388103244503</v>
+        <v>1.568643131573103</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.8478290928448589</v>
+        <v>-0.6126553548146241</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6204</v>
+        <v>6224</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>822.0442205927203</v>
+        <v>1001.390361383917</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>64.96154520839954</v>
+        <v>56.46115057973169</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>43.13048904176055</v>
+        <v>26.33481500025108</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.9770393097248764</v>
+        <v>1.522114344626562</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.33173563233923</v>
+        <v>-0.9532023182052892</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6274</v>
+        <v>6213</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>820.9664374104318</v>
+        <v>963.5549132650287</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1835</v>
+        <v>280</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>66.68743840544556</v>
+        <v>57.88347900932989</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>30.58558943295679</v>
+        <v>14.21304418676956</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.560392298439874</v>
+        <v>1.450135559536951</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-3.650961662488015</v>
+        <v>0.5184790487531818</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6177</v>
+        <v>6204</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>819.6961260733688</v>
+        <v>957.0442205927204</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>50.4</v>
+        <v>115</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>72.91478292036614</v>
+        <v>64.96154520371226</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>23.68861962017161</v>
+        <v>43.13048901184808</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.069612607336881</v>
+        <v>0.9770393097248764</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,11 +1100,11 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.6280708025398394</v>
+        <v>-0.3317356320911813</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>811.3457398527937</v>
+        <v>951.3457398527936</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>567</v>
@@ -1135,29 +1135,29 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>68.13150322804762</v>
+        <v>68.1315032380721</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>41.69714134088091</v>
+        <v>41.69714133231043</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0.7526059576892237</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.065863516942926</v>
+        <v>1.065863516752124</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>806.0797831708525</v>
+        <v>951.0797831708524</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>347.5</v>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>70.74679401029144</v>
+        <v>70.74679400296066</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46.03690667576743</v>
+        <v>46.03690663653261</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0.6862118344780277</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-1.137749826151634</v>
+        <v>-1.137749825483859</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6414</v>
+        <v>6243</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>798.3956259098907</v>
+        <v>936.5366190224228</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>383</v>
+        <v>34.9</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>56.74857677160591</v>
+        <v>59.46368103166919</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28.66995540315384</v>
+        <v>23.06370814425168</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.9660201683947672</v>
+        <v>2.427005682927047</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-2.666711116310081</v>
+        <v>0.1063534210714067</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6465</v>
+        <v>6414</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>796.582399934118</v>
+        <v>918.4983997560332</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>71.2</v>
+        <v>383</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>71.52503933461486</v>
+        <v>56.74857678218378</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>27.77945844282979</v>
+        <v>28.66995543493741</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2.461989510598256</v>
+        <v>0.9748377156591762</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.866006900735168</v>
+        <v>-2.666711116596286</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6229</v>
+        <v>6269</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>785.1930796309306</v>
+        <v>892.6192287623436</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>27.75</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>56.69731771677132</v>
+        <v>65.00204505614371</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>14.25856403546298</v>
+        <v>27.92682152984781</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.414475385178861</v>
+        <v>1.60492315839094</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.0111740771819539</v>
+        <v>1.103197421643702</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6182</v>
+        <v>6239</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>775.9675268830841</v>
+        <v>892.2686977649745</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>120</v>
+        <v>363.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>74.80141097909939</v>
+        <v>62.752397676084</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>41.16547381028171</v>
+        <v>32.60204206762911</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3.184623933480305</v>
+        <v>1.791518730077329</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1.879788884102055</v>
+        <v>-1.8144425529742</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6213</v>
+        <v>6207</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>773.5515229824321</v>
+        <v>869.6622383409696</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>280</v>
+        <v>165.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>57.88347901364004</v>
+        <v>73.42437886451395</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>14.21304422893267</v>
+        <v>65.47352710864946</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.449833813856945</v>
+        <v>1.451130144977567</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.5184790484288182</v>
+        <v>1.871337730322537</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6202</v>
+        <v>6415</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>766.6413905764664</v>
+        <v>869.6215584665347</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>67</v>
+        <v>629</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>64.34662513109966</v>
+        <v>62.98330246476162</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>19.96449137277071</v>
+        <v>27.22784779362621</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.933771881274046</v>
+        <v>0.9194152094644874</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.102051007498679</v>
+        <v>-2.11316456237714</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6292</v>
+        <v>6271</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>763.0645320544089</v>
+        <v>859.2845795487885</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>67.8</v>
+        <v>242.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>65.08187360578286</v>
+        <v>57.46030391036047</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>35.28654255730599</v>
+        <v>26.39876838956524</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.8427035721046203</v>
+        <v>1.139376035142924</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.2688025362278656</v>
+        <v>-2.671035201220782</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6435</v>
+        <v>6229</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>756.9681281993547</v>
+        <v>805.1930796309306</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>317.5</v>
+        <v>27.75</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>68.49866230092807</v>
+        <v>56.69731772007886</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>27.62678611389062</v>
+        <v>14.25856412509739</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8660630388365577</v>
+        <v>2.414475385178861</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.0413874830717091</v>
+        <v>-0.0111740771247102</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6224</v>
+        <v>6449</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>756.3903613839167</v>
+        <v>799.7061429708505</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>85</v>
+        <v>433</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.46115057973169</v>
+        <v>64.83169484825201</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>26.33481498022689</v>
+        <v>45.88146755036836</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.522114344626562</v>
+        <v>3.883759940377382</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.9532023183865416</v>
+        <v>0.6318310174490307</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6432</v>
+        <v>6405</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>755.8391564370169</v>
+        <v>729.311351292448</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>73.64044534607476</v>
+        <v>55.60087816683525</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45.22865781625818</v>
+        <v>34.90184041484187</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.457904699323384</v>
+        <v>0.3217607544201292</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,11 +1736,11 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.8110939485947428</v>
+        <v>-1.970138863406501</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>57.22892807210492</v>
+        <v>57.22892806898532</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>29.05421616484603</v>
+        <v>29.05421618481638</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0.5892331880216267</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.068905431179449</v>
+        <v>0.06890543121761419</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6265</v>
+        <v>6409</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>720.7546546228652</v>
+        <v>724.3789285815665</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>57.6</v>
+        <v>926</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>57.42576674946682</v>
+        <v>63.60750589865238</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>34.27167415022459</v>
+        <v>36.81175997608579</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4577563870320194</v>
+        <v>0.350129008767992</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.4838794546326626</v>
+        <v>12.23868796819655</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6257</v>
+        <v>6168</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>719.0107113328063</v>
+        <v>692.081467153788</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>235</v>
+        <v>28.3</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>61.30340628238463</v>
+        <v>56.72702776360283</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>27.18010090197145</v>
+        <v>18.3079478221434</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.568643131573103</v>
+        <v>0.8038019187073308</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.6126553549100748</v>
+        <v>0.1922361349713824</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6239</v>
+        <v>6206</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>702.2565744654919</v>
+        <v>661.6612981735532</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>363.5</v>
+        <v>131.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>62.75239766595177</v>
+        <v>49.70981561662099</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>32.60204201788887</v>
+        <v>22.08548406705299</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.7906302834143</v>
+        <v>0.5194377813511825</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-1.814442552497226</v>
+        <v>-1.906749108293209</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6271</v>
+        <v>6223</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>699.2382163225967</v>
+        <v>660.8378807512632</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>242.5</v>
+        <v>6415</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>57.46030390610546</v>
+        <v>60.8304064615095</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>26.39876841164659</v>
+        <v>22.35129990396116</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.13538298128</v>
+        <v>0.5431049838496131</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-2.671035201697769</v>
+        <v>19.30534879781706</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6269</v>
+        <v>6282</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>692.6192287623436</v>
+        <v>649.0176738928537</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>58.1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>65.0020450659356</v>
+        <v>50.33080935538626</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>27.92682157428072</v>
+        <v>31.03284671126725</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.60492315839094</v>
+        <v>0.2618168626402428</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>1.103197421376584</v>
+        <v>-0.9485586938728584</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6243</v>
+        <v>6174</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>671.5366190224227</v>
+        <v>636.5079797377323</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>34.9</v>
+        <v>52.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>59.46368100144801</v>
+        <v>63.25992737357205</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>23.06370818160447</v>
+        <v>38.54871303266291</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.427005682927047</v>
+        <v>0.5606766846880814</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.1063534209950859</v>
+        <v>0.2011156554284228</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6207</v>
+        <v>6170</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>669.6622383409696</v>
+        <v>622.9631911426771</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>165.5</v>
+        <v>52.7</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>73.42437886735446</v>
+        <v>59.04937296044682</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>65.47352713954196</v>
+        <v>16.20894050861687</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.451130144977567</v>
+        <v>0.9061476844132113</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1.871337730217597</v>
+        <v>0.0240615450818624</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6223</v>
+        <v>6451</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>660.8284454965084</v>
+        <v>618.4884286772781</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>6415</v>
+        <v>561</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>60.83040646525512</v>
+        <v>51.27143809846531</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22.3512998998548</v>
+        <v>32.04958926709072</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5409883653005381</v>
+        <v>0.6628707409452409</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>19.30534879304795</v>
+        <v>-14.31537774400668</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6282</v>
+        <v>6277</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>649.0128179698166</v>
+        <v>606.4198153551597</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>58.1</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>50.33080934893073</v>
+        <v>43.34582340160882</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>31.03284673931548</v>
+        <v>34.04116985487811</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.2615310667091835</v>
+        <v>0.6915520244965411</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.9485586939396348</v>
+        <v>-0.7729174914882255</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6174</v>
+        <v>6283</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>636.5079797377323</v>
+        <v>581.2077747790513</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>52.3</v>
+        <v>24</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>63.25992737859279</v>
+        <v>48.76582534582401</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>38.54871303772756</v>
+        <v>17.24696428238789</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5606766846880814</v>
+        <v>0.4475167051748277</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.2011156553521003</v>
+        <v>-0.1543808270508213</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6449</v>
+        <v>6285</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>629.7061429708505</v>
+        <v>578.8105611293382</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>433</v>
+        <v>274</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>64.83169484874836</v>
+        <v>49.06072000834708</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45.88146757829183</v>
+        <v>23.61172889399182</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>3.883759940377382</v>
+        <v>0.7740685436572498</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.6318310170864976</v>
+        <v>-5.122666349408667</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6409</v>
+        <v>6190</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>619.3730402520765</v>
+        <v>564.7632801076418</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>926</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>63.6075059115061</v>
+        <v>56.43469967723286</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>36.81175996223282</v>
+        <v>27.58932173119373</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3434026030512185</v>
+        <v>0.7140799817735073</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>12.23868796056475</v>
+        <v>-0.7704641290944001</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6405</v>
+        <v>6164</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>619.311351292448</v>
+        <v>558.03170823345</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>71.5</v>
+        <v>13.35</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>55.60087815846247</v>
+        <v>57.36821633867488</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>34.90184040252356</v>
+        <v>18.64032408828005</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3217607544201292</v>
+        <v>0.8599950504678335</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-1.970138863492372</v>
+        <v>0.0676145471334869</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6470</v>
+        <v>6191</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>619.1897208947046</v>
+        <v>539.7431410270915</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>50</v>
+        <v>100.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>59.73318601045053</v>
+        <v>54.4935334860127</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>13.69816535789576</v>
+        <v>15.11159117250549</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5883573715655044</v>
+        <v>0.6616468660263307</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0241888991091245</v>
+        <v>0.6031270851233806</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6415</v>
+        <v>6215</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>569.6215584665347</v>
+        <v>534.636146048295</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>629</v>
+        <v>108.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>62.98330247464943</v>
+        <v>42.08268277977433</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>27.22784761240373</v>
+        <v>20.10059840216585</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9194152094644874</v>
+        <v>0.3520442224208299</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-2.11316456209093</v>
+        <v>-1.745787936742803</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6291</v>
+        <v>6214</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>568.3319817347277</v>
+        <v>524.3606477518807</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>548</v>
+        <v>142</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>51.41650328653378</v>
+        <v>56.90523708848229</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>23.09024451709832</v>
+        <v>21.50050850369227</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6006161432875079</v>
+        <v>0.9622407567563168</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-11.58880090309583</v>
+        <v>-0.9129699180816172</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6411</v>
+        <v>6227</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>560.2270641890661</v>
+        <v>514.7398336685904</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>106.5</v>
+        <v>122</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>65.89631589892878</v>
+        <v>49.74638377758803</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>29.84763161651309</v>
+        <v>25.44446024220813</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.062454686067277</v>
+        <v>0.2650141710535298</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.1860637148641273</v>
+        <v>-2.096496070684819</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6285</v>
+        <v>6244</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>558.8105611293382</v>
+        <v>509.775281053682</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>274</v>
+        <v>28.45</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>49.06071999904941</v>
+        <v>46.33816062991882</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>23.61172887509831</v>
+        <v>21.20703170431941</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7740685436572498</v>
+        <v>0.7515454038426383</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-5.122666349599462</v>
+        <v>-0.1411212760441181</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6472</v>
+        <v>6438</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>554.8037189056299</v>
+        <v>509.2225607957296</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>422.5</v>
+        <v>159</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>62.69955756516925</v>
+        <v>49.23644497282319</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.92122193399657</v>
+        <v>26.03585446807615</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.7874910525721692</v>
+        <v>1.069043533916673</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>7.70378938029202</v>
+        <v>-0.0334307106791103</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6270</v>
+        <v>6245</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>554.2826470499921</v>
+        <v>491.4005002910672</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>35.15</v>
+        <v>81.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>63.19135382813523</v>
+        <v>43.77435949418707</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45.41022799230429</v>
+        <v>19.89417660145157</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.352970536786362</v>
+        <v>0.3411948422338942</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.1890281645908977</v>
+        <v>-1.011497065343512</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6419</v>
+        <v>6225</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>552.2053107919629</v>
+        <v>490.1167412871322</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>149.5</v>
+        <v>24</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>54.37552163060887</v>
+        <v>49.68011510821749</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>15.0738591231403</v>
+        <v>13.90348947477653</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.732889291287575</v>
+        <v>1.002665472684152</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1668670259857793</v>
+        <v>-0.1598012872464848</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6206</v>
+        <v>6217</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>551.6612981735534</v>
+        <v>457.4856184533021</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>131.5</v>
+        <v>247</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.70981564824098</v>
+        <v>47.17034481591806</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.08548400842745</v>
+        <v>13.7229382695485</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5194377813511825</v>
+        <v>1.286508909919002</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-1.906749108961019</v>
+        <v>-3.512012036478051</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6190</v>
+        <v>6233</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>544.7632801076418</v>
+        <v>455.7221287063966</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>25.05</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>56.43469968239722</v>
+        <v>50.68150451088698</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>27.58932173884769</v>
+        <v>14.65834172730783</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7140799817735073</v>
+        <v>1.297064337841194</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.7704641291230254</v>
+        <v>0.0455995666723988</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6214</v>
+        <v>6205</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>523.3851959739635</v>
+        <v>436.4945939956356</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>142</v>
+        <v>81.3</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>56.90523711252445</v>
+        <v>50.09626962005607</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>21.5005083769532</v>
+        <v>14.61379071417942</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.894524135859685</v>
+        <v>0.2250804693705266</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.9129699187493624</v>
+        <v>-0.4202794006678314</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6227</v>
+        <v>6443</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>514.7398336685904</v>
+        <v>421.440696038927</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>122</v>
+        <v>39.35</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>49.74638372675257</v>
+        <v>47.25396531785737</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>25.44446033113892</v>
+        <v>19.38855771226062</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.2650141710535298</v>
+        <v>0.4134476688732886</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-2.096496071772352</v>
+        <v>-0.1373970729918484</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6170</v>
+        <v>6412</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>512.9631911426771</v>
+        <v>404.4517301800585</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>52.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>59.04937304456864</v>
+        <v>46.82229303689105</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.208940457123</v>
+        <v>22.46981954543356</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9061476844132113</v>
+        <v>0.8435962880298441</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0240615448910697</v>
+        <v>-1.252912005586311</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6244</v>
+        <v>6237</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>509.7763737757867</v>
+        <v>403.9372175121545</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>28.45</v>
+        <v>46</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>46.33816060751433</v>
+        <v>48.26178725094877</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>21.20703174256887</v>
+        <v>24.41562917378912</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7502112499124586</v>
+        <v>0.2429401649266979</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.141121276072735</v>
+        <v>-0.785282407439402</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6279</v>
+        <v>6278</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>508.8630430728085</v>
+        <v>397.1633209612489</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>120.5</v>
+        <v>204.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>54.3674795110712</v>
+        <v>50.62819149143812</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19.76578968048716</v>
+        <v>23.52487554835856</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.7591296678770422</v>
+        <v>0.4420690344958153</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.4236845655647503</v>
+        <v>-2.838809011847102</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6168</v>
+        <v>6230</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>507.081467153788</v>
+        <v>387.0122122471337</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>28.3</v>
+        <v>132.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>56.72702776115253</v>
+        <v>42.34871091058251</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>18.30794783309833</v>
+        <v>12.82831857471248</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.8038019187073308</v>
+        <v>0.8051375705832824</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.192236134914144</v>
+        <v>0.1673419178553947</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6451</v>
+        <v>6456</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>493.4884286772781</v>
+        <v>385.495090512279</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>561</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.27143811102688</v>
+        <v>51.6586538249236</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>32.04958942319817</v>
+        <v>13.52136209726946</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6628707409452409</v>
+        <v>0.3803803346381167</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-14.31537774543768</v>
+        <v>-0.7337911619781168</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6245</v>
+        <v>6185</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>491.4005002910672</v>
+        <v>384.3138403851283</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>81.5</v>
+        <v>14.25</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>43.77435943644984</v>
+        <v>52.96873026765213</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19.89417658401862</v>
+        <v>14.45750405487722</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3411948422338942</v>
+        <v>0.9570536285935184</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-1.011497065553372</v>
+        <v>-0.0013801881066551</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6225</v>
+        <v>6423</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>490.1167412871322</v>
+        <v>371.4012528753081</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>24</v>
+        <v>82.7</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.68011507420546</v>
+        <v>36.4284206309197</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>13.90348954835289</v>
+        <v>26.81017441571719</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.002665472684152</v>
+        <v>0.3713523152163033</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.1598012872369452</v>
+        <v>-0.5273955845391241</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6417</v>
+        <v>6416</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>489.3435385822784</v>
+        <v>367.9322199292531</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>132</v>
+        <v>83.7</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.82889183294753</v>
+        <v>44.51411698646536</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18.74335297652491</v>
+        <v>24.30526330639056</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4213280922531366</v>
+        <v>0.6341102215005354</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.73916496009064</v>
+        <v>-0.6349020224564862</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6283</v>
+        <v>6228</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>471.2077747790513</v>
+        <v>361.9648452128129</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>24</v>
+        <v>20.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>48.76582543124842</v>
+        <v>47.31780110296714</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>17.24696423826892</v>
+        <v>3.554323688635285</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4475167051748277</v>
+        <v>2.495324724186391</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.1543808272034527</v>
+        <v>-0.0343201661573043</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6263</v>
+        <v>6426</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>462.7507579797932</v>
+        <v>353.3015929125629</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>165</v>
+        <v>210.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.52735246721761</v>
+        <v>44.19433046180282</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>17.69578605662793</v>
+        <v>21.60059969106866</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.7442202653832513</v>
+        <v>0.6506505153093213</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-2.00940414351116</v>
+        <v>-5.314858149180882</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6261</v>
+        <v>6210</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>451.4509727146504</v>
+        <v>349.5070856528575</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>98.8</v>
+        <v>20.7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>43.91844125872084</v>
+        <v>47.86099490361656</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>24.31691139161276</v>
+        <v>18.46732722671644</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.3414767950837476</v>
+        <v>0.1978360894148916</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.833529617651421</v>
+        <v>-0.0923582275356761</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6205</v>
+        <v>6198</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>446.4945939956356</v>
+        <v>348.7508838373458</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>81.3</v>
+        <v>20.95</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>50.09626961388816</v>
+        <v>51.58829564721799</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>14.61379070207098</v>
+        <v>8.630317987701792</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.2250804693705266</v>
+        <v>0.296927920135825</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.4202794007918478</v>
+        <v>0.5156006098520409</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6485</v>
+        <v>6192</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>444.4771880803901</v>
+        <v>330.2361069412211</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>88.40000000000001</v>
+        <v>117.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>42.57386921775211</v>
+        <v>38.81477499257372</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>21.45851347895683</v>
+        <v>25.86037428965153</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.2945648800002804</v>
+        <v>0.3145181069467326</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-2.872026323613124</v>
+        <v>-1.521128999806879</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6164</v>
+        <v>6218</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>443.03170823345</v>
+        <v>327.7815343980197</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>13.35</v>
+        <v>35.15</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>57.36821634476357</v>
+        <v>47.14613767057866</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.64032410656493</v>
+        <v>12.25542911822255</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.8599950504678335</v>
+        <v>0.4424165379367363</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.06761454710486781</v>
+        <v>-0.2344542557244631</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6184</v>
+        <v>6165</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>441.2731196875166</v>
+        <v>319.6410563706847</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>46.95</v>
+        <v>48.6</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>57.65312429866638</v>
+        <v>48.47703570062512</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>28.53115210565143</v>
+        <v>19.66677800090942</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.258401108815607</v>
+        <v>0.6366206423168603</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1106727212616683</v>
+        <v>-0.0044790315061577</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6464</v>
+        <v>6234</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>424.9112140750763</v>
+        <v>315.4385298327895</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>78</v>
+        <v>45.1</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>60.85130967515415</v>
+        <v>47.74012029432568</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>14.16808789715576</v>
+        <v>19.00541864031957</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.1016077762154038</v>
+        <v>0.6476143978223299</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0608904758554187</v>
+        <v>-0.5944284198718233</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6191</v>
+        <v>6167</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>424.7431410270914</v>
+        <v>312.8943096051412</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>100.5</v>
+        <v>12.15</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>54.49353346021711</v>
+        <v>52.79264135882173</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15.11159116660686</v>
+        <v>13.72606257247504</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6616468660263307</v>
+        <v>0.6325730982500021</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.60312708495166</v>
+        <v>0.0555787277858198</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6215</v>
+        <v>6183</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>424.6361460482953</v>
+        <v>309.6868737615495</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>108.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>42.08268277601394</v>
+        <v>47.62506660520302</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>20.10059840121153</v>
+        <v>17.53627713352513</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3520442224208299</v>
+        <v>0.4569077437802262</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-1.745787936780958</v>
+        <v>0.110767052481834</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6277</v>
+        <v>6222</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>421.4198153551598</v>
+        <v>302.2626252517844</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>20.55</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>43.34582340696603</v>
+        <v>46.82500689980459</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>34.04116987732547</v>
+        <v>24.9481752845211</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6915520244965411</v>
+        <v>2.071822970836187</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.7729174915263779</v>
+        <v>0.024239185997297</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6412</v>
+        <v>6203</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>419.4517301800585</v>
+        <v>290.0818917123524</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>91.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.82229304773184</v>
+        <v>42.6737760220299</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>22.46981944354099</v>
+        <v>22.9286905805637</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.8435962880298441</v>
+        <v>0.5777424047316947</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.252912005967906</v>
+        <v>-0.4978940567552774</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6278</v>
+        <v>6226</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>412.1395646636555</v>
+        <v>289.7693731460059</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>204.5</v>
+        <v>12.4</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.62819148342396</v>
+        <v>46.82242054278706</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>23.524875520573</v>
+        <v>14.38642873543796</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4396934047364716</v>
+        <v>0.428733510601494</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-2.838809012037895</v>
+        <v>-0.115236816573651</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6237</v>
+        <v>6188</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>403.9372175121545</v>
+        <v>268.163588856006</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>46</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.26178726101108</v>
+        <v>42.5318580596587</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>24.41562920352005</v>
+        <v>12.76928073137325</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.2429401649266979</v>
+        <v>0.3816469564370702</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.7852824076015776</v>
+        <v>-0.3492583333440251</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6418</v>
+        <v>6176</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>393.7955054996802</v>
+        <v>264.4087783821619</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>31.65</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>49.83115253994374</v>
+        <v>32.68446738096738</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>25.36268785394281</v>
+        <v>30.17179788439309</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4226349640389737</v>
+        <v>1.181063212391341</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0334594569346899</v>
+        <v>-1.354137689003721</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6284</v>
+        <v>6272</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>392.7381228165822</v>
+        <v>261.3647643529146</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>106</v>
+        <v>32.1</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>54.57505718637391</v>
+        <v>39.79388107063368</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>43.65177857148863</v>
+        <v>27.70211978292175</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.094680520487123</v>
+        <v>0.5277712131334709</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-1.003040975879391</v>
+        <v>-0.6779261325818076</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6290</v>
+        <v>6281</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>379.4541069414162</v>
+        <v>257.6347822378845</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>319.5</v>
+        <v>51.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>54.76479611366676</v>
+        <v>51.25014382956702</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>17.6734622918094</v>
+        <v>12.71512595080126</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.092674892508752</v>
+        <v>0.6136536692550163</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-5.310635816894594</v>
+        <v>0.0983302280199211</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6246</v>
+        <v>6235</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>377.7481964883071</v>
+        <v>238.856409976988</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>15.45</v>
+        <v>40.55</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.75350371223846</v>
+        <v>42.47922285931555</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.82743538774891</v>
+        <v>17.35099953332482</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.242980157244478</v>
+        <v>0.3317982064039533</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.006172388550468</v>
+        <v>-0.2017834169697767</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6426</v>
+        <v>6216</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>373.301592912563</v>
+        <v>234.0119752524716</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>210.5</v>
+        <v>23.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>44.19433044768755</v>
+        <v>51.83617426903396</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>21.60059968983916</v>
+        <v>18.7238691123942</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6506505153093213</v>
+        <v>1.230427000489724</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-5.314858149409835</v>
+        <v>0.07791982839243849</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6423</v>
+        <v>6201</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>371.4012528753081</v>
+        <v>219.4612327894723</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>82.7</v>
+        <v>48.4</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>36.42842058557154</v>
+        <v>50.480389891953</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>26.81017440450253</v>
+        <v>19.23264952321172</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3713523152163033</v>
+        <v>0.9016623020152086</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.5273955841384632</v>
+        <v>0.1082492922924083</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6416</v>
+        <v>6194</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>367.9322199292532</v>
+        <v>179.9840446133515</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>83.7</v>
+        <v>32.4</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.51411701344828</v>
+        <v>42.77047145833025</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>24.30526327453534</v>
+        <v>18.66848142689972</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6341102215005354</v>
+        <v>0.3310630412043693</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.6349020229334776</v>
+        <v>-0.1682952330965333</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6185</v>
+        <v>6477</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>364.3138403851283</v>
+        <v>163.0710536074495</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>14.25</v>
+        <v>32.05</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>52.96873032140641</v>
+        <v>42.61291740183095</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.45750404062718</v>
+        <v>13.3672670562329</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.9570536285935184</v>
+        <v>0.454664544342417</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,1866 +4704,11 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.001380188144814</v>
+        <v>-0.1184032833188974</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>6228</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>全譜</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D81" s="2" t="n">
-        <v>361.9648452128162</v>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>47.31780144086481</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>3.554323559671483</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>2.495324724186391</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N81" s="2" t="n">
-        <v>-0.0343201670540438</v>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>6474</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>華豫寧</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>351.1608024044791</v>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>51.68217887735757</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>19.82052206033141</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>1.410562888220116</v>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N82" s="2" t="n">
-        <v>-0.1690497816669633</v>
-      </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>6210</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>慶生</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>349.5070856528575</v>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>47.86099484892759</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>18.46732713772921</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>0.1978360894148916</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N83" s="2" t="n">
-        <v>-0.0923582275261333</v>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>6198</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>瑞築</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>348.750883837346</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>20.95</v>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>51.58829565729454</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>8.630317979987909</v>
-      </c>
-      <c r="J84" s="2" t="n">
-        <v>0.296927920135825</v>
-      </c>
-      <c r="K84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N84" s="2" t="n">
-        <v>0.5156006096994061</v>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>6217</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>中探針</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>342.485618453302</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>247</v>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>47.17034481572545</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>13.7229382695485</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>1.286508909919002</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N85" s="2" t="n">
-        <v>-3.512012036563868</v>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>6233</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>旺玖</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D86" s="2" t="n">
-        <v>340.7221287063966</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>25.05</v>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>50.68150448016481</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>14.65834173408222</v>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>1.297064337841194</v>
-      </c>
-      <c r="K86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N86" s="2" t="n">
-        <v>0.0455995666056228</v>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>6443</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>元晶</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>331.440696038927</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>39.35</v>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>47.25396533546858</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>19.38855772480326</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>0.4134476688732886</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N87" s="2" t="n">
-        <v>-0.1373970731063258</v>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>6462</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>神盾</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>328.3799044892616</v>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>43.59728085126296</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>21.7291445090313</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>0.3231326070144807</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N88" s="2" t="n">
-        <v>-0.852283577998405</v>
-      </c>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>6165</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>浪凡</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>319.6410563706847</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>48.47703570062512</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>19.66677803152092</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>0.6366206423168603</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N89" s="2" t="n">
-        <v>-0.0044790314489231</v>
-      </c>
-      <c r="O89" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>6275</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>元山</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>318.7030974950343</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>42.56678454037492</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>19.5177468882004</v>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>0.3573991734040693</v>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N90" s="2" t="n">
-        <v>-0.1918914978087105</v>
-      </c>
-      <c r="O90" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>6234</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>高僑</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>315.4385298327895</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>47.74012030976572</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>19.00541862475837</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>0.6476143978223299</v>
-      </c>
-      <c r="K91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N91" s="2" t="n">
-        <v>-0.5944284200339967</v>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>6192</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>巨路</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D92" s="2" t="n">
-        <v>315.2361069412211</v>
-      </c>
-      <c r="E92" s="2" t="n">
-        <v>117.5</v>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>38.81477496104471</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>25.86037428965153</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>0.3145181069467326</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N92" s="2" t="n">
-        <v>-1.521128999902249</v>
-      </c>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>6222</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>立軒</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D93" s="2" t="n">
-        <v>302.2626252517844</v>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>46.82501113228233</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>24.94817514725367</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>2.071822970836187</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N93" s="2" t="n">
-        <v>0.0242391859877592</v>
-      </c>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>6438</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>迅得</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D94" s="2" t="n">
-        <v>294.2225607957297</v>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>49.23644495898201</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>26.03585446295379</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>1.069043533916673</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N94" s="2" t="n">
-        <v>-0.0334307108698963</v>
-      </c>
-      <c r="O94" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>6203</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>海韻電</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D95" s="2" t="n">
-        <v>290.0818917123524</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>42.6737760220299</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>22.92869051238163</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>0.5777424047316947</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N95" s="2" t="n">
-        <v>-0.4978940569842233</v>
-      </c>
-      <c r="O95" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>6226</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>光鼎</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>289.7693731460059</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>46.82242056179856</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>14.38642873543796</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>0.428733510601494</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N96" s="2" t="n">
-        <v>-0.1152368166041779</v>
-      </c>
-      <c r="O96" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
-        <v>6230</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>尼得科超眾</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D97" s="2" t="n">
-        <v>277.0122122471337</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>42.34871091966678</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>12.82831857400152</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>0.8051375705832824</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N97" s="2" t="n">
-        <v>0.1673419170922301</v>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
-        <v>6188</v>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>廣明</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>268.163588856006</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>42.53185807325703</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>12.76928070817457</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>0.3816469564370702</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N98" s="2" t="n">
-        <v>-0.3492583336683708</v>
-      </c>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
-        <v>6272</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>驊陞</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>261.3647643529146</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>39.7938811249438</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>27.70211968297593</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>0.5277712131334709</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N99" s="2" t="n">
-        <v>-0.677926132782145</v>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
-        <v>6281</v>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>全國電</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>257.6347822378845</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>51.25014379956159</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>12.71512572768712</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>0.6136536692550163</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>0.0983302279245305</v>
-      </c>
-      <c r="O100" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
-        <v>6456</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>GIS-KY</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>255.495090512279</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>51.65865381494955</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>13.52136205964908</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>0.3803803346381167</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>-0.7337911622070603</v>
-      </c>
-      <c r="O101" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, above_ichimoku_cloud</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
-        <v>6176</v>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>瑞儀</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>244.408778382162</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>32.6844672767678</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>30.17179784332511</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>1.181063212391341</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N102" s="2" t="n">
-        <v>-1.354137687286569</v>
-      </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
-        <v>6216</v>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>居易</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>244.0119752524715</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>51.83617430523496</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>18.72386910494896</v>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>1.230427000489724</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N103" s="2" t="n">
-        <v>0.07791982830657899</v>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>6235</v>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>華孚</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D104" s="2" t="n">
-        <v>238.8564099769881</v>
-      </c>
-      <c r="E104" s="2" t="n">
-        <v>40.55</v>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>42.47922281089749</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>17.35099948634243</v>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>0.3317982064039533</v>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N104" s="2" t="n">
-        <v>-0.2017834171987307</v>
-      </c>
-      <c r="O104" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
-        <v>6183</v>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>關貿</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D105" s="2" t="n">
-        <v>234.6868737615495</v>
-      </c>
-      <c r="E105" s="2" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>47.62506654472218</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>17.53627714121469</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>0.4569077437802262</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N105" s="2" t="n">
-        <v>0.1107670526535411</v>
-      </c>
-      <c r="O105" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>6201</v>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>亞弘電</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>219.4612327894723</v>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>50.48038986766589</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>19.23264945617317</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>0.9016623020152086</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N106" s="2" t="n">
-        <v>0.1082492922924083</v>
-      </c>
-      <c r="O106" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
-        <v>6167</v>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>久正</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>202.8943096051413</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>52.79264132809526</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>13.72606248619434</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>0.6325730982500021</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N107" s="2" t="n">
-        <v>0.055578727442481</v>
-      </c>
-      <c r="O107" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>6287</v>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>元隆</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D108" s="2" t="n">
-        <v>202.1213010770209</v>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>51.71399387501272</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>0.9711762243867564</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>0.3819364013941486</v>
-      </c>
-      <c r="K108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N108" s="2" t="n">
-        <v>-0.0153085825903483</v>
-      </c>
-      <c r="O108" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, avoid_chase, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>6266</v>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>泰詠</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D109" s="2" t="n">
-        <v>194.4054500180727</v>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>37.96677032620119</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>23.07291967753642</v>
-      </c>
-      <c r="J109" s="2" t="n">
-        <v>1.103115124962853</v>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N109" s="2" t="n">
-        <v>-0.2166937203640647</v>
-      </c>
-      <c r="O109" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>6441</v>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>廣錠</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D110" s="2" t="n">
-        <v>190.3766423227635</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>44.16350250954222</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>12.02024968693589</v>
-      </c>
-      <c r="J110" s="2" t="n">
-        <v>0.263003004226627</v>
-      </c>
-      <c r="K110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N110" s="2" t="n">
-        <v>-0.1793538076740327</v>
-      </c>
-      <c r="O110" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
-        <v>6218</v>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>豪勉</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D111" s="2" t="n">
-        <v>187.7815343980197</v>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>35.15</v>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>47.14613774439317</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>12.25542909620091</v>
-      </c>
-      <c r="J111" s="2" t="n">
-        <v>0.4424165379367363</v>
-      </c>
-      <c r="K111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N111" s="2" t="n">
-        <v>-0.2344542560869796</v>
-      </c>
-      <c r="O111" s="2" t="inlineStr">
-        <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
-        <v>6477</v>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>安集</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D112" s="2" t="n">
-        <v>163.0710536074495</v>
-      </c>
-      <c r="E112" s="2" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>42.61291739417285</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>13.36726706178081</v>
-      </c>
-      <c r="J112" s="2" t="n">
-        <v>0.454664544342417</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N112" s="2" t="n">
-        <v>-0.1184032833570573</v>
-      </c>
-      <c r="O112" s="2" t="inlineStr">
-        <is>
           <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>6194</v>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>育富</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D113" s="2" t="n">
-        <v>159.9840446133515</v>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>42.77047138853931</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>18.6684814018688</v>
-      </c>
-      <c r="J113" s="2" t="n">
-        <v>0.3310630412043693</v>
-      </c>
-      <c r="K113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N113" s="2" t="n">
-        <v>-0.168295233153773</v>
-      </c>
-      <c r="O113" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
-        <v>6236</v>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>中湛</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>130.8713210110822</v>
-      </c>
-      <c r="E114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>48.02625861030701</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>8.123428603714771</v>
-      </c>
-      <c r="J114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N114" s="2" t="n">
-        <v>-0.4180897594202955</v>
-      </c>
-      <c r="O114" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, obv_uptrend</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
-        <v>6276</v>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>安鈦克</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>75.75612026988469</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>35.82295329689545</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>19.93433297989875</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>1.034477761634004</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" s="2" t="n">
-        <v>-0.0271087090214681</v>
-      </c>
-      <c r="O115" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq6_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq6_2026-06-18.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6175</v>
+        <v>6446</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1281.88137953711</v>
+        <v>1323.214537947204</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>114</v>
+        <v>1060</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>65.85770210235331</v>
+        <v>74.09915146700037</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>41.4854619749655</v>
+        <v>40.63522493182666</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.872381972630764</v>
+        <v>0.8778045481982885</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1030614984289304</v>
+        <v>3.156858670960105</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6166</v>
+        <v>6175</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1259.613134038523</v>
+        <v>1281.88137953711</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>155.5</v>
+        <v>114</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>71.83714697168239</v>
+        <v>65.85770210235331</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>61.77269413266056</v>
+        <v>41.4854619749655</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.625049938328196</v>
+        <v>1.872381972630764</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2684405774413232</v>
+        <v>0.1030614984289304</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6182</v>
+        <v>6166</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1090.972985131049</v>
+        <v>1259.613134038523</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>120</v>
+        <v>155.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>74.80141097666259</v>
+        <v>71.83714697168239</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>41.16547377113102</v>
+        <v>61.77269413266056</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.185114777399742</v>
+        <v>1.625049938328196</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.879788884226068</v>
+        <v>0.2684405774413232</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6220</v>
+        <v>6274</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1080.102355728493</v>
+        <v>1210.966437410432</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>38.35</v>
+        <v>1835</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.96435200147269</v>
+        <v>66.68743840395511</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>52.69632016694276</v>
+        <v>30.58558936923232</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.110235572849227</v>
+        <v>0.560392298439874</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.3932672571252598</v>
+        <v>-3.650961660961613</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6208</v>
+        <v>6259</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1070.263952910117</v>
+        <v>1119.953639568867</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>99</v>
+        <v>35.85</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>59.43824753028846</v>
+        <v>74.09447066284378</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>24.93777213134326</v>
+        <v>47.28967303855775</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.93263461349321</v>
+        <v>2.095363956886709</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2644630702497279</v>
+        <v>0.6590754801553913</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6209</v>
+        <v>6182</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1050.633881032445</v>
+        <v>1090.972985131049</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>97.09999999999999</v>
+        <v>120</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>66.2170962499149</v>
+        <v>74.80141097666259</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>38.65150830177213</v>
+        <v>41.16547377113102</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.163388103244503</v>
+        <v>3.185114777399742</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.8478290929879462</v>
+        <v>1.879788884226068</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6202</v>
+        <v>6220</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1041.641390576467</v>
+        <v>1080.102355728493</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>67</v>
+        <v>38.35</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>64.34662512514765</v>
+        <v>68.96435200147269</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>19.9644913956534</v>
+        <v>52.69632016694276</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.933771881274046</v>
+        <v>2.110235572849227</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.10205100765132</v>
+        <v>0.3932672571252598</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6257</v>
+        <v>6208</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1004.010711332806</v>
+        <v>1070.263952910117</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>235</v>
+        <v>99</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>61.30340628238463</v>
+        <v>59.43824753028846</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>27.18010090578662</v>
+        <v>24.93777213134326</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.568643131573103</v>
+        <v>3.93263461349321</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.6126553548146241</v>
+        <v>0.2644630702497279</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6224</v>
+        <v>6432</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1001.390361383917</v>
+        <v>1065.839156437017</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>85</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.46115057973169</v>
+        <v>73.6404453481843</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>26.33481500025108</v>
+        <v>45.22865783408803</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.522114344626562</v>
+        <v>1.457904699323384</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,84 +994,84 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.9532023182052892</v>
+        <v>0.8110939485851958</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6213</v>
+        <v>6288</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>963.5549132650287</v>
+        <v>1053.76371134358</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>280</v>
+        <v>24.25</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>57.88347900932989</v>
+        <v>66.44292918989618</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>14.21304418676956</v>
+        <v>25.33459642290103</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.450135559536951</v>
+        <v>3.476371134358034</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.5184790487531818</v>
+        <v>0.1959970559887558</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6204</v>
+        <v>6209</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>957.0442205927204</v>
+        <v>1050.633881032445</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>115</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>64.96154520371226</v>
+        <v>66.2170962499149</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>43.13048901184808</v>
+        <v>38.65150830177213</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.9770393097248764</v>
+        <v>1.163388103244503</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.3317356320911813</v>
+        <v>0.8478290929879462</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6196</v>
+        <v>6202</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>951.3457398527936</v>
+        <v>1041.641390576467</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>567</v>
+        <v>67</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>68.1315032380721</v>
+        <v>64.34662512514765</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>41.69714133231043</v>
+        <v>19.9644913956534</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.7526059576892237</v>
+        <v>1.933771881274046</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.065863516752124</v>
+        <v>1.10205100765132</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6197</v>
+        <v>6257</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>951.0797831708524</v>
+        <v>1004.010711332806</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>347.5</v>
+        <v>235</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>70.74679400296066</v>
+        <v>61.30340628238463</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46.03690663653261</v>
+        <v>27.18010090578662</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6862118344780277</v>
+        <v>1.568643131573103</v>
       </c>
       <c r="K14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-1.137749825483859</v>
+        <v>-0.6126553548146241</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6243</v>
+        <v>6224</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>936.5366190224228</v>
+        <v>1001.390361383917</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>34.9</v>
+        <v>85</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>59.46368103166919</v>
+        <v>56.46115057973169</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>23.06370814425168</v>
+        <v>26.33481500025108</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.427005682927047</v>
+        <v>1.522114344626562</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>2</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.1063534210714067</v>
+        <v>-0.9532023182052892</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6414</v>
+        <v>6465</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>918.4983997560332</v>
+        <v>996.582399934118</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>383</v>
+        <v>71.2</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.74857678218378</v>
+        <v>71.52503933461486</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>28.66995543493741</v>
+        <v>27.77945864404654</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.9748377156591762</v>
+        <v>2.461989510598256</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-2.666711116596286</v>
+        <v>1.866006900833259</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6269</v>
+        <v>6213</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>892.6192287623436</v>
+        <v>963.5549132650287</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>280</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>65.00204505614371</v>
+        <v>57.88347900932989</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>27.92682152984781</v>
+        <v>14.21304418676956</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.60492315839094</v>
+        <v>1.450135559536951</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.103197421643702</v>
+        <v>0.5184790487531818</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6239</v>
+        <v>6204</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>892.2686977649745</v>
+        <v>957.0442205927204</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>363.5</v>
+        <v>115</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>62.752397676084</v>
+        <v>64.96154520371226</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>32.60204206762911</v>
+        <v>43.13048901184808</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.791518730077329</v>
+        <v>0.9770393097248764</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-1.8144425529742</v>
+        <v>-0.3317356320911813</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6207</v>
+        <v>6435</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>869.6622383409696</v>
+        <v>956.9681281993549</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>165.5</v>
+        <v>317.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>73.42437886451395</v>
+        <v>68.49866230038037</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>65.47352710864946</v>
+        <v>27.62678609593646</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.451130144977567</v>
+        <v>0.8660630388365577</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.871337730322537</v>
+        <v>-0.0413874826900659</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6415</v>
+        <v>6196</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>869.6215584665347</v>
+        <v>951.3457398527936</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>629</v>
+        <v>567</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>62.98330246476162</v>
+        <v>68.1315032380721</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>27.22784779362621</v>
+        <v>41.69714133231043</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.9194152094644874</v>
+        <v>0.7526059576892237</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-2.11316456237714</v>
+        <v>1.065863516752124</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6271</v>
+        <v>6197</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>859.2845795487885</v>
+        <v>951.0797831708524</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>242.5</v>
+        <v>347.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>57.46030391036047</v>
+        <v>70.74679400296066</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>26.39876838956524</v>
+        <v>46.03690663653261</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.139376035142924</v>
+        <v>0.6862118344780277</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-2.671035201220782</v>
+        <v>-1.137749825483859</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6229</v>
+        <v>6243</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>805.1930796309306</v>
+        <v>936.5366190224228</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>27.75</v>
+        <v>34.9</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>56.69731772007886</v>
+        <v>59.46368103166919</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>14.25856412509739</v>
+        <v>23.06370814425168</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.414475385178861</v>
+        <v>2.427005682927047</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>2</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.0111740771247102</v>
+        <v>0.1063534210714067</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6449</v>
+        <v>6292</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>799.7061429708505</v>
+        <v>933.0645320544088</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>433</v>
+        <v>67.8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>64.83169484825201</v>
+        <v>65.0818735972651</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45.88146755036836</v>
+        <v>35.28654244933107</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>3.883759940377382</v>
+        <v>0.8427035721046203</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.6318310174490307</v>
+        <v>0.268802536418665</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6405</v>
+        <v>6414</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>729.311351292448</v>
+        <v>918.4983997560332</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>71.5</v>
+        <v>383</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>55.60087816683525</v>
+        <v>56.74857678218378</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>34.90184041484187</v>
+        <v>28.66995543493741</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.3217607544201292</v>
+        <v>0.9748377156591762</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>3</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-1.970138863406501</v>
+        <v>-2.666711116596286</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6189</v>
+        <v>6269</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>727.8923318802163</v>
+        <v>892.6192287623436</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>54.9</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>57.22892806898532</v>
+        <v>65.00204505614371</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>29.05421618481638</v>
+        <v>27.92682152984781</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5892331880216267</v>
+        <v>1.60492315839094</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.06890543121761419</v>
+        <v>1.103197421643702</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6409</v>
+        <v>6239</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>724.3789285815665</v>
+        <v>892.2686977649745</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>926</v>
+        <v>363.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>63.60750589865238</v>
+        <v>62.752397676084</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>36.81175997608579</v>
+        <v>32.60204206762911</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.350129008767992</v>
+        <v>1.791518730077329</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>12.23868796819655</v>
+        <v>-1.8144425529742</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6168</v>
+        <v>6207</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>692.081467153788</v>
+        <v>869.6622383409696</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>28.3</v>
+        <v>165.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>56.72702776360283</v>
+        <v>73.42437886451395</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>18.3079478221434</v>
+        <v>65.47352710864946</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8038019187073308</v>
+        <v>1.451130144977567</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1922361349713824</v>
+        <v>1.871337730322537</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6206</v>
+        <v>6415</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>661.6612981735532</v>
+        <v>869.6215584665347</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>131.5</v>
+        <v>629</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>49.70981561662099</v>
+        <v>62.98330246476162</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>22.08548406705299</v>
+        <v>27.22784779362621</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5194377813511825</v>
+        <v>0.9194152094644874</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-1.906749108293209</v>
+        <v>-2.11316456237714</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6223</v>
+        <v>6271</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>660.8378807512632</v>
+        <v>859.2845795487885</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>6415</v>
+        <v>242.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>60.8304064615095</v>
+        <v>57.46030391036047</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>22.35129990396116</v>
+        <v>26.39876838956524</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.5431049838496131</v>
+        <v>1.139376035142924</v>
       </c>
       <c r="K29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>19.30534879781706</v>
+        <v>-2.671035201220782</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6282</v>
+        <v>6411</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>649.0176738928537</v>
+        <v>840.2270641890661</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>58.1</v>
+        <v>106.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.33080935538626</v>
+        <v>65.89631590472192</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>31.03284671126725</v>
+        <v>29.8476316049158</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.2618168626402428</v>
+        <v>1.062454686067277</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.9485586938728584</v>
+        <v>-0.1860637145016106</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6174</v>
+        <v>6177</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>636.5079797377323</v>
+        <v>809.6961260733688</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>52.3</v>
+        <v>50.4</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>63.25992737357205</v>
+        <v>72.91478290627504</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>38.54871303266291</v>
+        <v>23.68861961753688</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5606766846880814</v>
+        <v>3.069612607336881</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.2011156554284228</v>
+        <v>0.6280708025303064</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6170</v>
+        <v>6229</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>622.9631911426771</v>
+        <v>805.1930796309306</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>52.7</v>
+        <v>27.75</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>59.04937296044682</v>
+        <v>56.69731772007886</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>16.20894050861687</v>
+        <v>14.25856412509739</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.9061476844132113</v>
+        <v>2.414475385178861</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0240615450818624</v>
+        <v>-0.0111740771247102</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6451</v>
+        <v>6472</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>618.4884286772781</v>
+        <v>799.8037189056297</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>561</v>
+        <v>422.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>51.27143809846531</v>
+        <v>62.69955753601445</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>32.04958926709072</v>
+        <v>22.92122198079601</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6628707409452409</v>
+        <v>0.7874910525721692</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-14.31537774400668</v>
+        <v>7.703789382772356</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6277</v>
+        <v>6449</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>606.4198153551597</v>
+        <v>799.7061429708505</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>433</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>43.34582340160882</v>
+        <v>64.83169484825201</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>34.04116985487811</v>
+        <v>45.88146755036836</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.6915520244965411</v>
+        <v>3.883759940377382</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.7729174914882255</v>
+        <v>0.6318310174490307</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6283</v>
+        <v>6405</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>581.2077747790513</v>
+        <v>729.311351292448</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>24</v>
+        <v>71.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>48.76582534582401</v>
+        <v>55.60087816683525</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.24696428238789</v>
+        <v>34.90184041484187</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4475167051748277</v>
+        <v>0.3217607544201292</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.1543808270508213</v>
+        <v>-1.970138863406501</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6285</v>
+        <v>6189</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>578.8105611293382</v>
+        <v>727.8923318802163</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>274</v>
+        <v>54.9</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>49.06072000834708</v>
+        <v>57.22892806898532</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23.61172889399182</v>
+        <v>29.05421618481638</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7740685436572498</v>
+        <v>0.5892331880216267</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-5.122666349408667</v>
+        <v>0.06890543121761419</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6190</v>
+        <v>6409</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>564.7632801076418</v>
+        <v>724.3789285815665</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>926</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>56.43469967723286</v>
+        <v>63.60750589865238</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>27.58932173119373</v>
+        <v>36.81175997608579</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.7140799817735073</v>
+        <v>0.350129008767992</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.7704641290944001</v>
+        <v>12.23868796819655</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6164</v>
+        <v>6265</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>558.03170823345</v>
+        <v>720.7546546228652</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>13.35</v>
+        <v>57.6</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>57.36821633867488</v>
+        <v>57.42576674887235</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18.64032408828005</v>
+        <v>34.27167414211916</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.8599950504678335</v>
+        <v>0.4577563870320194</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0676145471334869</v>
+        <v>-0.4838794545983167</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6191</v>
+        <v>6291</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>539.7431410270915</v>
+        <v>708.3319817347276</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>100.5</v>
+        <v>548</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.4935334860127</v>
+        <v>51.41650328616583</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15.11159117250549</v>
+        <v>23.09024441455405</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.6616468660263307</v>
+        <v>0.6006161432875079</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.6031270851233806</v>
+        <v>-11.58880090267614</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6215</v>
+        <v>6168</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>534.636146048295</v>
+        <v>692.081467153788</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>108.5</v>
+        <v>28.3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>42.08268277977433</v>
+        <v>56.72702776360283</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20.10059840216585</v>
+        <v>18.3079478221434</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3520442224208299</v>
+        <v>0.8038019187073308</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.745787936742803</v>
+        <v>0.1922361349713824</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6214</v>
+        <v>6206</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>524.3606477518807</v>
+        <v>661.6612981735532</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>142</v>
+        <v>131.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>56.90523708848229</v>
+        <v>49.70981561662099</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>21.50050850369227</v>
+        <v>22.08548406705299</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9622407567563168</v>
+        <v>0.5194377813511825</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.9129699180816172</v>
+        <v>-1.906749108293209</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6227</v>
+        <v>6223</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>514.7398336685904</v>
+        <v>660.8378807512632</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>122</v>
+        <v>6415</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>49.74638377758803</v>
+        <v>60.8304064615095</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25.44446024220813</v>
+        <v>22.35129990396116</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.2650141710535298</v>
+        <v>0.5431049838496131</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>1</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-2.096496070684819</v>
+        <v>19.30534879781706</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6244</v>
+        <v>6282</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>509.775281053682</v>
+        <v>649.0176738928537</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>28.45</v>
+        <v>58.1</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>46.33816062991882</v>
+        <v>50.33080935538626</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>21.20703170431941</v>
+        <v>31.03284671126725</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7515454038426383</v>
+        <v>0.2618168626402428</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.1411212760441181</v>
+        <v>-0.9485586938728584</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6438</v>
+        <v>6470</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>509.2225607957296</v>
+        <v>639.1897208947051</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>159</v>
+        <v>50</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.23644497282319</v>
+        <v>59.73318600641904</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>26.03585446807615</v>
+        <v>13.69816543068332</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.069043533916673</v>
+        <v>0.5883573715655044</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0334307106791103</v>
+        <v>0.0241888992522207</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6245</v>
+        <v>6174</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>491.4005002910672</v>
+        <v>636.5079797377323</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>81.5</v>
+        <v>52.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>43.77435949418707</v>
+        <v>63.25992737357205</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>19.89417660145157</v>
+        <v>38.54871303266291</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3411948422338942</v>
+        <v>0.5606766846880814</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.011497065343512</v>
+        <v>0.2011156554284228</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6225</v>
+        <v>6170</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>490.1167412871322</v>
+        <v>622.9631911426771</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>24</v>
+        <v>52.7</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>49.68011510821749</v>
+        <v>59.04937296044682</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>13.90348947477653</v>
+        <v>16.20894050861687</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.002665472684152</v>
+        <v>0.9061476844132113</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1598012872464848</v>
+        <v>0.0240615450818624</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6217</v>
+        <v>6451</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>457.4856184533021</v>
+        <v>618.4884286772781</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>247</v>
+        <v>561</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>47.17034481591806</v>
+        <v>51.27143809846531</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>13.7229382695485</v>
+        <v>32.04958926709072</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.286508909919002</v>
+        <v>0.6628707409452409</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-3.512012036478051</v>
+        <v>-14.31537774400668</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6233</v>
+        <v>6277</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>455.7221287063966</v>
+        <v>606.4198153551597</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>25.05</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>50.68150451088698</v>
+        <v>43.34582340160882</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>14.65834172730783</v>
+        <v>34.04116985487811</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.297064337841194</v>
+        <v>0.6915520244965411</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0455995666723988</v>
+        <v>-0.7729174914882255</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6205</v>
+        <v>6283</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>436.4945939956356</v>
+        <v>581.2077747790513</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>81.3</v>
+        <v>24</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>50.09626962005607</v>
+        <v>48.76582534582401</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>14.61379071417942</v>
+        <v>17.24696428238789</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2250804693705266</v>
+        <v>0.4475167051748277</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.4202794006678314</v>
+        <v>-0.1543808270508213</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6443</v>
+        <v>6285</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>421.440696038927</v>
+        <v>578.8105611293382</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>39.35</v>
+        <v>274</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.25396531785737</v>
+        <v>49.06072000834708</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.38855771226062</v>
+        <v>23.61172889399182</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4134476688732886</v>
+        <v>0.7740685436572498</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.1373970729918484</v>
+        <v>-5.122666349408667</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6412</v>
+        <v>6190</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>404.4517301800585</v>
+        <v>564.7632801076418</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>91.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46.82229303689105</v>
+        <v>56.43469967723286</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>22.46981954543356</v>
+        <v>27.58932173119373</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.8435962880298441</v>
+        <v>0.7140799817735073</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-1.252912005586311</v>
+        <v>-0.7704641290944001</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6237</v>
+        <v>6164</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>403.9372175121545</v>
+        <v>558.03170823345</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>46</v>
+        <v>13.35</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>48.26178725094877</v>
+        <v>57.36821633867488</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>24.41562917378912</v>
+        <v>18.64032408828005</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.2429401649266979</v>
+        <v>0.8599950504678335</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.785282407439402</v>
+        <v>0.0676145471334869</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6278</v>
+        <v>6270</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>397.1633209612489</v>
+        <v>554.2826470499921</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>204.5</v>
+        <v>35.15</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.62819149143812</v>
+        <v>63.19135385367504</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>23.52487554835856</v>
+        <v>45.41022798030216</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4420690344958153</v>
+        <v>0.352970536786362</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-2.838809011847102</v>
+        <v>0.1890281646004377</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6230</v>
+        <v>6419</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>387.0122122471337</v>
+        <v>552.2053107919629</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>132.5</v>
+        <v>149.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>42.34871091058251</v>
+        <v>54.37552167716878</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12.82831857471248</v>
+        <v>15.07385921706488</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.8051375705832824</v>
+        <v>1.732889291287575</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.1673419178553947</v>
+        <v>-0.1668670259285528</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6456</v>
+        <v>6191</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>385.495090512279</v>
+        <v>539.7431410270915</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>100.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.6586538249236</v>
+        <v>54.4935334860127</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>13.52136209726946</v>
+        <v>15.11159117250549</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.3803803346381167</v>
+        <v>0.6616468660263307</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.7337911619781168</v>
+        <v>0.6031270851233806</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6185</v>
+        <v>6215</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>384.3138403851283</v>
+        <v>534.636146048295</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>14.25</v>
+        <v>108.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>52.96873026765213</v>
+        <v>42.08268277977433</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14.45750405487722</v>
+        <v>20.10059840216585</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9570536285935184</v>
+        <v>0.3520442224208299</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0013801881066551</v>
+        <v>-1.745787936742803</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6423</v>
+        <v>6279</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>371.4012528753081</v>
+        <v>528.8630430728085</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>82.7</v>
+        <v>120.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>36.4284206309197</v>
+        <v>54.3674795743669</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>26.81017441571719</v>
+        <v>19.76578968048716</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3713523152163033</v>
+        <v>0.7591296678770422</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.5273955845391241</v>
+        <v>-0.4236845655647503</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6416</v>
+        <v>6214</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>367.9322199292531</v>
+        <v>524.3606477518807</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>83.7</v>
+        <v>142</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>44.51411698646536</v>
+        <v>56.90523708848229</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>24.30526330639056</v>
+        <v>21.50050850369227</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6341102215005354</v>
+        <v>0.9622407567563168</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.6349020224564862</v>
+        <v>-0.9129699180816172</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6228</v>
+        <v>6227</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>361.9648452128129</v>
+        <v>514.7398336685904</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>20.5</v>
+        <v>122</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>47.31780110296714</v>
+        <v>49.74638377758803</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>3.554323688635285</v>
+        <v>25.44446024220813</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.495324724186391</v>
+        <v>0.2650141710535298</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0343201661573043</v>
+        <v>-2.096496070684819</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6426</v>
+        <v>6244</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>353.3015929125629</v>
+        <v>509.775281053682</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>210.5</v>
+        <v>28.45</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>44.19433046180282</v>
+        <v>46.33816062991882</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>21.60059969106866</v>
+        <v>21.20703170431941</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6506505153093213</v>
+        <v>0.7515454038426383</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-5.314858149180882</v>
+        <v>-0.1411212760441181</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6210</v>
+        <v>6438</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>349.5070856528575</v>
+        <v>509.2225607957296</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>20.7</v>
+        <v>159</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>47.86099490361656</v>
+        <v>49.23644497282319</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>18.46732722671644</v>
+        <v>26.03585446807615</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.1978360894148916</v>
+        <v>1.069043533916673</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0923582275356761</v>
+        <v>-0.0334307106791103</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6198</v>
+        <v>6284</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>348.7508838373458</v>
+        <v>507.7381228165822</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>20.95</v>
+        <v>106</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.58829564721799</v>
+        <v>54.57505716563964</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>8.630317987701792</v>
+        <v>43.65177860548686</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.296927920135825</v>
+        <v>1.094680520487123</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.5156006098520409</v>
+        <v>-1.003040975383323</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6192</v>
+        <v>6245</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>330.2361069412211</v>
+        <v>491.4005002910672</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>117.5</v>
+        <v>81.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>38.81477499257372</v>
+        <v>43.77435949418707</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>25.86037428965153</v>
+        <v>19.89417660145157</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3145181069467326</v>
+        <v>0.3411948422338942</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-1.521128999806879</v>
+        <v>-1.011497065343512</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6218</v>
+        <v>6225</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>327.7815343980197</v>
+        <v>490.1167412871322</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>35.15</v>
+        <v>24</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.14613767057866</v>
+        <v>49.68011510821749</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.25542911822255</v>
+        <v>13.90348947477653</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4424165379367363</v>
+        <v>1.002665472684152</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.2344542557244631</v>
+        <v>-0.1598012872464848</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6165</v>
+        <v>6417</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>319.6410563706847</v>
+        <v>489.3435385822784</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>48.6</v>
+        <v>132</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>48.47703570062512</v>
+        <v>48.82889183143813</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>19.66677800090942</v>
+        <v>18.74335294372348</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6366206423168603</v>
+        <v>0.4213280922531366</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0044790315061577</v>
+        <v>-1.739164960071542</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6234</v>
+        <v>6261</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>315.4385298327895</v>
+        <v>471.4509727146504</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>45.1</v>
+        <v>98.8</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.74012029432568</v>
+        <v>43.91844125352781</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>19.00541864031957</v>
+        <v>24.31691140269249</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.6476143978223299</v>
+        <v>0.3414767950837476</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.5944284198718233</v>
+        <v>-1.833529617498796</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6167</v>
+        <v>6263</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>312.8943096051412</v>
+        <v>462.7507579797932</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>12.15</v>
+        <v>165</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>52.79264135882173</v>
+        <v>50.52735247274278</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>13.72606257247504</v>
+        <v>17.69578617224071</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6325730982500021</v>
+        <v>0.7442202653832513</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0555787277858198</v>
+        <v>-2.009404143034196</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6183</v>
+        <v>6217</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>309.6868737615495</v>
+        <v>457.4856184533021</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>90.40000000000001</v>
+        <v>247</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>47.62506660520302</v>
+        <v>47.17034481591806</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>17.53627713352513</v>
+        <v>13.7229382695485</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4569077437802262</v>
+        <v>1.286508909919002</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.110767052481834</v>
+        <v>-3.512012036478051</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6222</v>
+        <v>6233</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>302.2626252517844</v>
+        <v>455.7221287063966</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>20.55</v>
+        <v>25.05</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>46.82500689980459</v>
+        <v>50.68150451088698</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>24.9481752845211</v>
+        <v>14.65834172730783</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.071822970836187</v>
+        <v>1.297064337841194</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.024239185997297</v>
+        <v>0.0455995666723988</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6203</v>
+        <v>6485</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>290.0818917123524</v>
+        <v>444.4771880803901</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>67.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>42.6737760220299</v>
+        <v>42.57386915943968</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>22.9286905805637</v>
+        <v>21.45851349427728</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5777424047316947</v>
+        <v>0.2945648800002804</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.4978940567552774</v>
+        <v>-2.872026322811781</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6226</v>
+        <v>6184</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>289.7693731460059</v>
+        <v>441.2731196875169</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>12.4</v>
+        <v>46.95</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>46.82242054278706</v>
+        <v>57.65312429866638</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>14.38642873543796</v>
+        <v>28.53115205920032</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.428733510601494</v>
+        <v>1.258401108815607</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.115236816573651</v>
+        <v>0.1106727212998288</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6188</v>
+        <v>6205</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>268.163588856006</v>
+        <v>436.4945939956356</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>42.5318580596587</v>
+        <v>50.09626962005607</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12.76928073137325</v>
+        <v>14.61379071417942</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.3816469564370702</v>
+        <v>0.2250804693705266</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.3492583333440251</v>
+        <v>-0.4202794006678314</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6176</v>
+        <v>6464</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>264.4087783821619</v>
+        <v>424.9112140750763</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>87.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>32.68446738096738</v>
+        <v>60.85130971522322</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>30.17179788439309</v>
+        <v>14.16808793269412</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.181063212391341</v>
+        <v>0.1016077762154038</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.354137689003721</v>
+        <v>-0.0608904758554187</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6272</v>
+        <v>6443</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>261.3647643529146</v>
+        <v>421.440696038927</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>32.1</v>
+        <v>39.35</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>39.79388107063368</v>
+        <v>47.25396531785737</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>27.70211978292175</v>
+        <v>19.38855771226062</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5277712131334709</v>
+        <v>0.4134476688732886</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.6779261325818076</v>
+        <v>-0.1373970729918484</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6281</v>
+        <v>6412</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>257.6347822378845</v>
+        <v>404.4517301800585</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>51.5</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>51.25014382956702</v>
+        <v>46.82229303689105</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>12.71512595080126</v>
+        <v>22.46981954543356</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.6136536692550163</v>
+        <v>0.8435962880298441</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0983302280199211</v>
+        <v>-1.252912005586311</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6235</v>
+        <v>6237</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>238.856409976988</v>
+        <v>403.9372175121545</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>40.55</v>
+        <v>46</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>42.47922285931555</v>
+        <v>48.26178725094877</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>17.35099953332482</v>
+        <v>24.41562917378912</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3317982064039533</v>
+        <v>0.2429401649266979</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.2017834169697767</v>
+        <v>-0.785282407439402</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6216</v>
+        <v>6278</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>234.0119752524716</v>
+        <v>397.1633209612489</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>23.2</v>
+        <v>204.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>51.83617426903396</v>
+        <v>50.62819149143812</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.7238691123942</v>
+        <v>23.52487554835856</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.230427000489724</v>
+        <v>0.4420690344958153</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.07791982839243849</v>
+        <v>-2.838809011847102</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6201</v>
+        <v>6418</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>219.4612327894723</v>
+        <v>393.7955054996802</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>48.4</v>
+        <v>31.65</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>50.480389891953</v>
+        <v>49.83115250716641</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19.23264952321172</v>
+        <v>25.36268788865778</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.9016623020152086</v>
+        <v>0.4226349640389737</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.1082492922924083</v>
+        <v>0.0334594570587044</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6194</v>
+        <v>6230</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>179.9840446133515</v>
+        <v>387.0122122471337</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>32.4</v>
+        <v>132.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>42.77047145833025</v>
+        <v>42.34871091058251</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.66848142689972</v>
+        <v>12.82831857471248</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3310630412043693</v>
+        <v>0.8051375705832824</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,64 +4651,1919 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.1682952330965333</v>
+        <v>0.1673419178553947</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
+        <v>6456</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>GIS-KY</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>385.495090512279</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>51.6586538249236</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>13.52136209726946</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.3803803346381167</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>-0.7337911619781168</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>6185</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>幃翔</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>384.3138403851283</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>52.96873026765213</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>14.45750405487722</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.9570536285935184</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>-0.0013801881066551</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>6290</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>良維</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>379.4541069414162</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>319.5</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>54.76479611233262</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>17.6734622575771</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>1.092674892508752</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>-5.310635816493919</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>6246</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>臺龍</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>377.7481964883064</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>47.75350337473119</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>16.8274353109648</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>1.242980157244478</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>-0.0061723883119758</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>6423</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>億而得-創</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>371.4012528753081</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>36.4284206309197</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>26.81017441571719</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.3713523152163033</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>-0.5273955845391241</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>6416</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>瑞祺電通</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>367.9322199292531</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>44.51411698646536</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>24.30526330639056</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>0.6341102215005354</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>-0.6349020224564862</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>6228</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>全譜</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>361.9648452128129</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>47.31780110296714</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>3.554323688635285</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>2.495324724186391</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>-0.0343201661573043</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>6426</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>統新</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>353.3015929125629</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>44.19433046180282</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>21.60059969106866</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.6506505153093213</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>-5.314858149180882</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>華豫寧</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>351.1608024044791</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>51.68217887279506</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>19.82052206275499</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>1.410562888220116</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>-0.1690497816383418</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>慶生</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>349.5070856528575</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>47.86099490361656</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>18.46732722671644</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.1978360894148916</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>-0.0923582275356761</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>6198</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>瑞築</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>348.7508838373458</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>51.58829564721799</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>8.630317987701792</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.296927920135825</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>0.5156006098520409</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>6462</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>神盾</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>348.3799044892617</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>43.59728093992544</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>21.72914451870028</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.3231326070144807</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>-0.8522835780747307</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>6192</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>330.2361069412211</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>38.81477499257372</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>25.86037428965153</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.3145181069467326</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>-1.521128999806879</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>6218</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>豪勉</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>327.7815343980197</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>47.14613767057866</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>12.25542911822255</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.4424165379367363</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>-0.2344542557244631</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>6165</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>浪凡</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>319.6410563706847</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>48.47703570062512</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>19.66677800090942</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.6366206423168603</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>-0.0044790315061577</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>6275</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>元山</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>318.7030974950343</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>42.56678449594168</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>19.5177468715911</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.3573991734040693</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>-0.1918914975225163</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>6234</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>高僑</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>315.4385298327895</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>47.74012029432568</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>19.00541864031957</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.6476143978223299</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>-0.5944284198718233</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>6167</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>久正</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>312.8943096051412</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>52.79264135882173</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>13.72606257247504</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.6325730982500021</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>0.0555787277858198</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>6183</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>關貿</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>309.6868737615495</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>47.62506660520302</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>17.53627713352513</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0.4569077437802262</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>0.110767052481834</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>6222</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>立軒</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>302.2626252517844</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>46.82500689980459</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>24.9481752845211</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>2.071822970836187</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>0.024239185997297</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>海韻電</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>290.0818917123524</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>42.6737760220299</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>22.9286905805637</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.5777424047316947</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>-0.4978940567552774</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>6226</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>光鼎</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>289.7693731460059</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>46.82242054278706</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>14.38642873543796</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.428733510601494</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>-0.115236816573651</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>6188</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>廣明</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>268.163588856006</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>42.5318580596587</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>12.76928073137325</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.3816469564370702</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>-0.3492583333440251</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>6176</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>瑞儀</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>264.4087783821619</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>32.68446738096738</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>30.17179788439309</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>1.181063212391341</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-1.354137689003721</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>6272</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>驊陞</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>261.3647643529146</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>39.79388107063368</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>27.70211978292175</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.5277712131334709</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>-0.6779261325818076</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>6281</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>全國電</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>257.6347822378845</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>51.25014382956702</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>12.71512595080126</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0.6136536692550163</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>0.0983302280199211</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>6235</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>華孚</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>238.856409976988</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>42.47922285931555</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>17.35099953332482</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.3317982064039533</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>-0.2017834169697767</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>6216</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>居易</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>234.0119752524716</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>51.83617426903396</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>18.7238691123942</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>1.230427000489724</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>0.07791982839243849</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>亞弘電</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>219.4612327894723</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>50.480389891953</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>19.23264952321172</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.9016623020152086</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>0.1082492922924083</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>6266</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>泰詠</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>214.4054500180726</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>37.96677026267143</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>23.072919675255</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>1.103115124962853</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>-0.2166937202305087</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>6287</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>元隆</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>201.9607418165609</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>51.71399387501272</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>0.9711762243867542</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.3819364013941486</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>-0.0153085825903483</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>6441</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>廣錠</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>190.3766423227635</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>44.16350254118422</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>12.02024966490627</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.263003004226627</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>-0.1793538076358711</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>6194</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>育富</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>179.9840446133515</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>42.77047145833025</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>18.66848142689972</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.3310630412043693</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>-0.1682952330965333</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
         <v>6477</v>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>安集</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D80" s="2" t="n">
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
         <v>163.0710536074495</v>
       </c>
-      <c r="E80" s="2" t="n">
+      <c r="E113" s="2" t="n">
         <v>32.05</v>
       </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H80" s="2" t="n">
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
         <v>42.61291740183095</v>
       </c>
-      <c r="I80" s="2" t="n">
+      <c r="I113" s="2" t="n">
         <v>13.3672670562329</v>
       </c>
-      <c r="J80" s="2" t="n">
+      <c r="J113" s="2" t="n">
         <v>0.454664544342417</v>
       </c>
-      <c r="K80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N80" s="2" t="n">
+      <c r="K113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
         <v>-0.1184032833188974</v>
       </c>
-      <c r="O80" s="2" t="inlineStr">
+      <c r="O113" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>6236</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>中湛</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>130.8713210110821</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>48.02625824486407</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>8.123429820350362</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.41808975409713</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>6276</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>安鈦克</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>75.75612026988472</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>35.82295323345136</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>19.93433313455046</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>1.034477761634004</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.0271087085063232</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
